--- a/data/downloads/YqE4iJYJbHkQcRC8ZxcdtHtL.xlsx
+++ b/data/downloads/YqE4iJYJbHkQcRC8ZxcdtHtL.xlsx
@@ -4485,7 +4485,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Crude long COVID incidence proportion among COVID-19-positive adults, N3C computable phenotype (2020-2023): the document reports 10.2% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
+          <t>Crude long COVID incidence proportion among COVID-19-positive adults, N3C computable phenotype (2020-2023): the document reports 10.2% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. The survey has no data for 2020, 2021. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Crude long COVID incidence proportion among COVID-19-positive adults, PCORnet computable phenotype (2020-2023): the document reports 25.9% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is inside the published 95% interval of at least one survey wave. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
+          <t>Crude long COVID incidence proportion among COVID-19-positive adults, PCORnet computable phenotype (2020-2023): the document reports 25.9% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is inside the published 95% interval of at least one survey wave. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. The survey has no data for 2020, 2021. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Harmonized NASEM-aligned long COVID incidence proportion among COVID-19-positive adults, N3C (2020-2023): the document reports 12.6% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
+          <t>Harmonized NASEM-aligned long COVID incidence proportion among COVID-19-positive adults, N3C (2020-2023): the document reports 12.6% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. The survey has no data for 2020, 2021. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>Harmonized NASEM-aligned long COVID incidence proportion among COVID-19-positive adults, PCORnet (2020-2023): the document reports 9.6% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
+          <t>Harmonized NASEM-aligned long COVID incidence proportion among COVID-19-positive adults, PCORnet (2020-2023): the document reports 9.6% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 18 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. The survey has no data for 2020, 2021. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
         </is>
       </c>
     </row>
